--- a/backend/arq/search_artists_drake.xlsx
+++ b/backend/arq/search_artists_drake.xlsx
@@ -49,15 +49,15 @@
     <t>https://api.spotify.com/v1/artists/2YZyLoL8N0Wb9xBt1NhZWg</t>
   </si>
   <si>
+    <t>https://api.spotify.com/v1/artists/5K4W6rqBFWDnAN6FQUkS6x</t>
+  </si>
+  <si>
+    <t>https://api.spotify.com/v1/artists/03ilIKH0i08IxmjKcn63ne</t>
+  </si>
+  <si>
     <t>https://api.spotify.com/v1/artists/06HL4z0CvFAxyc27GXpf02</t>
   </si>
   <si>
-    <t>https://api.spotify.com/v1/artists/5K4W6rqBFWDnAN6FQUkS6x</t>
-  </si>
-  <si>
-    <t>https://api.spotify.com/v1/artists/03ilIKH0i08IxmjKcn63ne</t>
-  </si>
-  <si>
     <t>https://api.spotify.com/v1/artists/4mskfuiHWZ3nX3qAdeaGiR</t>
   </si>
   <si>
@@ -79,15 +79,15 @@
     <t>2YZyLoL8N0Wb9xBt1NhZWg</t>
   </si>
   <si>
+    <t>5K4W6rqBFWDnAN6FQUkS6x</t>
+  </si>
+  <si>
+    <t>03ilIKH0i08IxmjKcn63ne</t>
+  </si>
+  <si>
     <t>06HL4z0CvFAxyc27GXpf02</t>
   </si>
   <si>
-    <t>5K4W6rqBFWDnAN6FQUkS6x</t>
-  </si>
-  <si>
-    <t>03ilIKH0i08IxmjKcn63ne</t>
-  </si>
-  <si>
     <t>4mskfuiHWZ3nX3qAdeaGiR</t>
   </si>
   <si>
@@ -109,15 +109,15 @@
     <t>[{'url': 'https://i.scdn.co/image/ab6761610000e5eb39ba6dcd4355c03de0b50918', 'height': 640, 'width': 640}, {'url': 'https://i.scdn.co/image/ab6761610000517439ba6dcd4355c03de0b50918', 'height': 320, 'width': 320}, {'url': 'https://i.scdn.co/image/ab6761610000f17839ba6dcd4355c03de0b50918', 'height': 160, 'width': 160}]</t>
   </si>
   <si>
+    <t>[{'url': 'https://i.scdn.co/image/ab6761610000e5eb6e835a500e791bf9c27a422a', 'height': 640, 'width': 640}, {'url': 'https://i.scdn.co/image/ab676161000051746e835a500e791bf9c27a422a', 'height': 320, 'width': 320}, {'url': 'https://i.scdn.co/image/ab6761610000f1786e835a500e791bf9c27a422a', 'height': 160, 'width': 160}]</t>
+  </si>
+  <si>
+    <t>[{'url': 'https://i.scdn.co/image/ab6761610000e5ebaa6e7bdc072605bb1c48adc2', 'height': 640, 'width': 640}, {'url': 'https://i.scdn.co/image/ab67616100005174aa6e7bdc072605bb1c48adc2', 'height': 320, 'width': 320}, {'url': 'https://i.scdn.co/image/ab6761610000f178aa6e7bdc072605bb1c48adc2', 'height': 160, 'width': 160}]</t>
+  </si>
+  <si>
     <t>[{'url': 'https://i.scdn.co/image/ab6761610000e5ebe2e8e7ff002a4afda1c7147e', 'height': 640, 'width': 640}, {'url': 'https://i.scdn.co/image/ab67616100005174e2e8e7ff002a4afda1c7147e', 'height': 320, 'width': 320}, {'url': 'https://i.scdn.co/image/ab6761610000f178e2e8e7ff002a4afda1c7147e', 'height': 160, 'width': 160}]</t>
   </si>
   <si>
-    <t>[{'url': 'https://i.scdn.co/image/ab6761610000e5eb6e835a500e791bf9c27a422a', 'height': 640, 'width': 640}, {'url': 'https://i.scdn.co/image/ab676161000051746e835a500e791bf9c27a422a', 'height': 320, 'width': 320}, {'url': 'https://i.scdn.co/image/ab6761610000f1786e835a500e791bf9c27a422a', 'height': 160, 'width': 160}]</t>
-  </si>
-  <si>
-    <t>[{'url': 'https://i.scdn.co/image/ab6761610000e5ebaa6e7bdc072605bb1c48adc2', 'height': 640, 'width': 640}, {'url': 'https://i.scdn.co/image/ab67616100005174aa6e7bdc072605bb1c48adc2', 'height': 320, 'width': 320}, {'url': 'https://i.scdn.co/image/ab6761610000f178aa6e7bdc072605bb1c48adc2', 'height': 160, 'width': 160}]</t>
-  </si>
-  <si>
     <t>[{'url': 'https://i.scdn.co/image/ab6761610000e5ebee551fdb982e8273349fb256', 'height': 640, 'width': 640}, {'url': 'https://i.scdn.co/image/ab67616100005174ee551fdb982e8273349fb256', 'height': 320, 'width': 320}, {'url': 'https://i.scdn.co/image/ab6761610000f178ee551fdb982e8273349fb256', 'height': 160, 'width': 160}]</t>
   </si>
   <si>
@@ -139,15 +139,15 @@
     <t>Kendrick Lamar</t>
   </si>
   <si>
+    <t>Kanye West</t>
+  </si>
+  <si>
+    <t>Drake Bell</t>
+  </si>
+  <si>
     <t>Taylor Swift</t>
   </si>
   <si>
-    <t>Kanye West</t>
-  </si>
-  <si>
-    <t>Drake Bell</t>
-  </si>
-  <si>
     <t>Drake Milligan</t>
   </si>
   <si>
@@ -172,15 +172,15 @@
     <t>spotify:artist:2YZyLoL8N0Wb9xBt1NhZWg</t>
   </si>
   <si>
+    <t>spotify:artist:5K4W6rqBFWDnAN6FQUkS6x</t>
+  </si>
+  <si>
+    <t>spotify:artist:03ilIKH0i08IxmjKcn63ne</t>
+  </si>
+  <si>
     <t>spotify:artist:06HL4z0CvFAxyc27GXpf02</t>
   </si>
   <si>
-    <t>spotify:artist:5K4W6rqBFWDnAN6FQUkS6x</t>
-  </si>
-  <si>
-    <t>spotify:artist:03ilIKH0i08IxmjKcn63ne</t>
-  </si>
-  <si>
     <t>spotify:artist:4mskfuiHWZ3nX3qAdeaGiR</t>
   </si>
   <si>
@@ -202,13 +202,13 @@
     <t>https://open.spotify.com/artist/2YZyLoL8N0Wb9xBt1NhZWg</t>
   </si>
   <si>
+    <t>https://open.spotify.com/artist/5K4W6rqBFWDnAN6FQUkS6x</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/artist/03ilIKH0i08IxmjKcn63ne</t>
+  </si>
+  <si>
     <t>https://open.spotify.com/artist/06HL4z0CvFAxyc27GXpf02</t>
-  </si>
-  <si>
-    <t>https://open.spotify.com/artist/5K4W6rqBFWDnAN6FQUkS6x</t>
-  </si>
-  <si>
-    <t>https://open.spotify.com/artist/03ilIKH0i08IxmjKcn63ne</t>
   </si>
   <si>
     <t>https://open.spotify.com/artist/4mskfuiHWZ3nX3qAdeaGiR</t>
